--- a/artfynd/A 58326-2024 artfynd.xlsx
+++ b/artfynd/A 58326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95741293</v>
+        <v>123924415</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,30 +929,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579319.4975775888</v>
+        <v>579454</v>
       </c>
       <c r="R4" t="n">
-        <v>6854679.926270043</v>
+        <v>6854701</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,27 +991,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-04-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-04-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Granlåga vid sjöstrand</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95741271</v>
+        <v>123924431</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579421.0741633367</v>
+        <v>579435</v>
       </c>
       <c r="R5" t="n">
-        <v>6854730.505119887</v>
+        <v>6854695</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,22 +1098,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-04-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-04-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,6 +1128,647 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123924519</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ålberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>579424</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6854721</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Delsbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123924446</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ålberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>579451</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6854700</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Delsbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123924449</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ålberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>579449</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6854706</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Delsbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123924422</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ålberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>579451</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6854701</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Delsbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123924494</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91435</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ålberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>579424</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6854721</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Delsbo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123924464</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ålberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>579433</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6854716</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Delsbo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58326-2024 artfynd.xlsx
+++ b/artfynd/A 58326-2024 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123924415</v>
+        <v>123924449</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579454</v>
+        <v>579449</v>
       </c>
       <c r="R4" t="n">
-        <v>6854701</v>
+        <v>6854706</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1027,7 +1027,7 @@
         <v>123924431</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123924519</v>
+        <v>123924446</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579424</v>
+        <v>579451</v>
       </c>
       <c r="R6" t="n">
-        <v>6854721</v>
+        <v>6854700</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123924446</v>
+        <v>123924422</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>579451</v>
       </c>
       <c r="R7" t="n">
-        <v>6854700</v>
+        <v>6854701</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123924449</v>
+        <v>123924494</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>91435</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,27 +1361,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1389,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579449</v>
+        <v>579424</v>
       </c>
       <c r="R8" t="n">
-        <v>6854706</v>
+        <v>6854721</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123924422</v>
+        <v>123924519</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579451</v>
+        <v>579424</v>
       </c>
       <c r="R9" t="n">
-        <v>6854701</v>
+        <v>6854721</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123924494</v>
+        <v>123924464</v>
       </c>
       <c r="B10" t="n">
-        <v>91435</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,26 +1574,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579424</v>
+        <v>579433</v>
       </c>
       <c r="R10" t="n">
-        <v>6854721</v>
+        <v>6854716</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123924464</v>
+        <v>123924415</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579433</v>
+        <v>579454</v>
       </c>
       <c r="R11" t="n">
-        <v>6854716</v>
+        <v>6854701</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 58326-2024 artfynd.xlsx
+++ b/artfynd/A 58326-2024 artfynd.xlsx
@@ -1345,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123924494</v>
+        <v>123924519</v>
       </c>
       <c r="B8" t="n">
-        <v>91435</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,26 +1361,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1451,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123924519</v>
+        <v>123924494</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>91435</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,27 +1468,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>

--- a/artfynd/A 58326-2024 artfynd.xlsx
+++ b/artfynd/A 58326-2024 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123924449</v>
+        <v>123924494</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>91435</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,27 +933,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579449</v>
+        <v>579424</v>
       </c>
       <c r="R4" t="n">
-        <v>6854706</v>
+        <v>6854721</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123924431</v>
+        <v>123924519</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1068,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579435</v>
+        <v>579424</v>
       </c>
       <c r="R5" t="n">
-        <v>6854695</v>
+        <v>6854721</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1238,7 +1237,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123924422</v>
+        <v>123924449</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1282,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579451</v>
+        <v>579449</v>
       </c>
       <c r="R7" t="n">
-        <v>6854701</v>
+        <v>6854706</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123924519</v>
+        <v>123924422</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1389,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579424</v>
+        <v>579451</v>
       </c>
       <c r="R8" t="n">
-        <v>6854721</v>
+        <v>6854701</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123924494</v>
+        <v>123924464</v>
       </c>
       <c r="B9" t="n">
-        <v>91435</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,26 +1467,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579424</v>
+        <v>579433</v>
       </c>
       <c r="R9" t="n">
-        <v>6854721</v>
+        <v>6854716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123924464</v>
+        <v>123924431</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579433</v>
+        <v>579435</v>
       </c>
       <c r="R10" t="n">
-        <v>6854716</v>
+        <v>6854695</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 58326-2024 artfynd.xlsx
+++ b/artfynd/A 58326-2024 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123924494</v>
+        <v>123924415</v>
       </c>
       <c r="B4" t="n">
-        <v>91435</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,26 +933,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579424</v>
+        <v>579454</v>
       </c>
       <c r="R4" t="n">
-        <v>6854721</v>
+        <v>6854701</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123924519</v>
+        <v>123924446</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1067,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579424</v>
+        <v>579451</v>
       </c>
       <c r="R5" t="n">
-        <v>6854721</v>
+        <v>6854700</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123924446</v>
+        <v>123924431</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1174,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579451</v>
+        <v>579435</v>
       </c>
       <c r="R6" t="n">
-        <v>6854700</v>
+        <v>6854695</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123924449</v>
+        <v>123924494</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>91435</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,27 +1254,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579449</v>
+        <v>579424</v>
       </c>
       <c r="R7" t="n">
-        <v>6854706</v>
+        <v>6854721</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123924422</v>
+        <v>123924519</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579451</v>
+        <v>579424</v>
       </c>
       <c r="R8" t="n">
-        <v>6854701</v>
+        <v>6854721</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123924464</v>
+        <v>123924449</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579433</v>
+        <v>579449</v>
       </c>
       <c r="R9" t="n">
-        <v>6854716</v>
+        <v>6854706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123924431</v>
+        <v>123924464</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579435</v>
+        <v>579433</v>
       </c>
       <c r="R10" t="n">
-        <v>6854695</v>
+        <v>6854716</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123924415</v>
+        <v>123924422</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579454</v>
+        <v>579451</v>
       </c>
       <c r="R11" t="n">
         <v>6854701</v>

--- a/artfynd/A 58326-2024 artfynd.xlsx
+++ b/artfynd/A 58326-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123924415</v>
+        <v>123924422</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579454</v>
+        <v>579451</v>
       </c>
       <c r="R4" t="n">
         <v>6854701</v>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123924449</v>
+        <v>123924464</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579449</v>
+        <v>579433</v>
       </c>
       <c r="R5" t="n">
-        <v>6854706</v>
+        <v>6854716</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123924431</v>
+        <v>123924415</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579435</v>
+        <v>579454</v>
       </c>
       <c r="R6" t="n">
-        <v>6854695</v>
+        <v>6854701</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123924446</v>
+        <v>123924449</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579451</v>
+        <v>579449</v>
       </c>
       <c r="R7" t="n">
-        <v>6854700</v>
+        <v>6854706</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123924519</v>
+        <v>123924494</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,27 +1361,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1452,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123924494</v>
+        <v>123924431</v>
       </c>
       <c r="B9" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,26 +1467,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579424</v>
+        <v>579435</v>
       </c>
       <c r="R9" t="n">
-        <v>6854721</v>
+        <v>6854695</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123924422</v>
+        <v>123924519</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579451</v>
+        <v>579424</v>
       </c>
       <c r="R10" t="n">
-        <v>6854701</v>
+        <v>6854721</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123924464</v>
+        <v>123924446</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579433</v>
+        <v>579451</v>
       </c>
       <c r="R11" t="n">
-        <v>6854716</v>
+        <v>6854700</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 58326-2024 artfynd.xlsx
+++ b/artfynd/A 58326-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123924422</v>
+        <v>123924431</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579451</v>
+        <v>579435</v>
       </c>
       <c r="R4" t="n">
-        <v>6854701</v>
+        <v>6854695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123924464</v>
+        <v>123924422</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579433</v>
+        <v>579451</v>
       </c>
       <c r="R5" t="n">
-        <v>6854716</v>
+        <v>6854701</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123924415</v>
+        <v>123924464</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579454</v>
+        <v>579433</v>
       </c>
       <c r="R6" t="n">
-        <v>6854701</v>
+        <v>6854716</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123924449</v>
+        <v>123924494</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,27 +1254,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579449</v>
+        <v>579424</v>
       </c>
       <c r="R7" t="n">
-        <v>6854706</v>
+        <v>6854721</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123924494</v>
+        <v>123924446</v>
       </c>
       <c r="B8" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,26 +1360,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579424</v>
+        <v>579451</v>
       </c>
       <c r="R8" t="n">
-        <v>6854721</v>
+        <v>6854700</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123924431</v>
+        <v>123924519</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579435</v>
+        <v>579424</v>
       </c>
       <c r="R9" t="n">
-        <v>6854695</v>
+        <v>6854721</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123924519</v>
+        <v>123924449</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579424</v>
+        <v>579449</v>
       </c>
       <c r="R10" t="n">
-        <v>6854721</v>
+        <v>6854706</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123924446</v>
+        <v>123924415</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579451</v>
+        <v>579454</v>
       </c>
       <c r="R11" t="n">
-        <v>6854700</v>
+        <v>6854701</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 58326-2024 artfynd.xlsx
+++ b/artfynd/A 58326-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123924431</v>
+        <v>123924449</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579435</v>
+        <v>579449</v>
       </c>
       <c r="R4" t="n">
-        <v>6854695</v>
+        <v>6854706</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123924422</v>
+        <v>123924446</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1071,7 +1071,7 @@
         <v>579451</v>
       </c>
       <c r="R5" t="n">
-        <v>6854701</v>
+        <v>6854700</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123924464</v>
+        <v>123924494</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,27 +1147,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579433</v>
+        <v>579424</v>
       </c>
       <c r="R6" t="n">
-        <v>6854716</v>
+        <v>6854721</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123924494</v>
+        <v>123924431</v>
       </c>
       <c r="B7" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,26 +1253,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579424</v>
+        <v>579435</v>
       </c>
       <c r="R7" t="n">
-        <v>6854721</v>
+        <v>6854695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123924446</v>
+        <v>123924415</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579451</v>
+        <v>579454</v>
       </c>
       <c r="R8" t="n">
-        <v>6854700</v>
+        <v>6854701</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123924519</v>
+        <v>123924464</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579424</v>
+        <v>579433</v>
       </c>
       <c r="R9" t="n">
-        <v>6854721</v>
+        <v>6854716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123924449</v>
+        <v>123924422</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579449</v>
+        <v>579451</v>
       </c>
       <c r="R10" t="n">
-        <v>6854706</v>
+        <v>6854701</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123924415</v>
+        <v>123924519</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579454</v>
+        <v>579424</v>
       </c>
       <c r="R11" t="n">
-        <v>6854701</v>
+        <v>6854721</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 58326-2024 artfynd.xlsx
+++ b/artfynd/A 58326-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123924449</v>
+        <v>123924519</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579449</v>
+        <v>579424</v>
       </c>
       <c r="R4" t="n">
-        <v>6854706</v>
+        <v>6854721</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123924446</v>
+        <v>123924449</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579451</v>
+        <v>579449</v>
       </c>
       <c r="R5" t="n">
-        <v>6854700</v>
+        <v>6854706</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123924494</v>
+        <v>123924464</v>
       </c>
       <c r="B6" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,26 +1147,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579424</v>
+        <v>579433</v>
       </c>
       <c r="R6" t="n">
-        <v>6854721</v>
+        <v>6854716</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123924431</v>
+        <v>123924415</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1281,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579435</v>
+        <v>579454</v>
       </c>
       <c r="R7" t="n">
-        <v>6854695</v>
+        <v>6854701</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123924415</v>
+        <v>123924494</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,27 +1361,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579454</v>
+        <v>579424</v>
       </c>
       <c r="R8" t="n">
-        <v>6854701</v>
+        <v>6854721</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123924464</v>
+        <v>123924431</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579433</v>
+        <v>579435</v>
       </c>
       <c r="R9" t="n">
-        <v>6854716</v>
+        <v>6854695</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123924519</v>
+        <v>123924446</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579424</v>
+        <v>579451</v>
       </c>
       <c r="R11" t="n">
-        <v>6854721</v>
+        <v>6854700</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
